--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -12,8 +12,8 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$157</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC157"/>
+  <dimension ref="A1:AC158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -831,20 +831,20 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>28680912</v>
+        <v>7010323</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>EmpowHer Toastmasters Club</t>
+          <t>ALTO Toastmasters Club</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -912,8 +912,8 @@
       <c r="W2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X2" s="9" t="n">
-        <v>0</v>
+      <c r="X2" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
@@ -924,8 +924,14 @@
       <c r="AA2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AB2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -939,15 +945,15 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>7010323</v>
+        <v>4106368</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>ALTO Toastmasters Club</t>
+          <t>Kotra Toastmasters Club</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -961,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -988,7 +994,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -999,36 +1005,36 @@
       <c r="S3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="9" t="n">
-        <v>0</v>
+      <c r="T3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -1044,11 +1050,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4106368</v>
+        <v>7315</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Kotra Toastmasters Club</t>
+          <t>Malacca Toastmasters Club</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -1066,17 +1072,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -1093,7 +1099,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -1104,38 +1110,34 @@
       <c r="S4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="10" t="n">
-        <v>1</v>
+      <c r="T4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>1</v>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X4" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Y4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1149,15 +1151,15 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7315</v>
+        <v>6756774</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Malacca Toastmasters Club</t>
+          <t>STMuar</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1171,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
@@ -1215,26 +1217,26 @@
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="10" t="n">
-        <v>4</v>
+      <c r="V5" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="10" t="n">
-        <v>6</v>
+      <c r="X5" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="10" t="n">
-        <v>1</v>
+      <c r="Z5" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="4" t="inlineStr"/>
     </row>
@@ -1246,19 +1248,19 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6756774</v>
+        <v>6912</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>STMuar</t>
+          <t>Famosa Toastmasters Club</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1272,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1299,7 +1301,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1317,25 +1319,25 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="9" t="n">
-        <v>0</v>
+      <c r="X6" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC6" s="4" t="inlineStr"/>
     </row>
@@ -1351,15 +1353,15 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6912</v>
+        <v>7860972</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Famosa Toastmasters Club</t>
+          <t>Melaka Bilingual Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1373,10 +1375,10 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -1400,7 +1402,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -1411,8 +1413,8 @@
       <c r="S7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="9" t="n">
-        <v>0</v>
+      <c r="T7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>0</v>
@@ -1424,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -1436,7 +1438,7 @@
         <v>1</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC7" s="4" t="inlineStr"/>
     </row>
@@ -1452,15 +1454,15 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7860972</v>
+        <v>28678781</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Melaka Bilingual Advanced Toastmasters Club</t>
+          <t>Micron Malaysia Toastmasters Club</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1474,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -1512,26 +1514,26 @@
       <c r="S8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="10" t="n">
-        <v>1</v>
+      <c r="T8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="10" t="n">
-        <v>7</v>
+      <c r="X8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="10" t="n">
-        <v>1</v>
+      <c r="Z8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1553,15 +1555,15 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>28678781</v>
+        <v>28678913</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Micron Malaysia Toastmasters Club</t>
+          <t>MUCM Research and Presentation</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1575,17 +1577,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
@@ -1602,7 +1604,7 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>0</v>
@@ -1620,27 +1622,31 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
+      <c r="X9" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1650,15 +1656,15 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>28678913</v>
+        <v>28678949</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>MUCM Research and Presentation</t>
+          <t>Infineon Melaka eXcellence Toastmasters Club</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
@@ -1676,10 +1682,10 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J10" s="4" t="n">
         <v>21</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>20</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>1</v>
@@ -1703,10 +1709,10 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -1727,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="X10" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -1739,11 +1745,11 @@
         <v>1</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -1759,11 +1765,11 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>28678949</v>
+        <v>4729722</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Infineon Melaka eXcellence Toastmasters Club</t>
+          <t>Infineon Melaka Toastmasters Club</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -1781,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1811,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -1826,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1844,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
@@ -1864,15 +1870,15 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4729722</v>
+        <v>6936825</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Infineon Melaka Toastmasters Club</t>
+          <t>MES Toastmasters Club</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1886,17 +1892,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1936,26 +1942,22 @@
       <c r="W12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X12" s="10" t="n">
-        <v>6</v>
+      <c r="X12" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="10" t="n">
-        <v>1</v>
+      <c r="Z12" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1969,11 +1971,11 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6936825</v>
+        <v>5163258</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>MES Toastmasters Club</t>
+          <t>MUCM Toastmasters Club</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
@@ -1991,17 +1993,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
@@ -2018,7 +2020,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>0</v>
@@ -2041,8 +2043,8 @@
       <c r="W13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X13" s="9" t="n">
-        <v>0</v>
+      <c r="X13" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>0</v>
@@ -2054,9 +2056,13 @@
         <v>1</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC13" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2066,19 +2072,19 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5163258</v>
+        <v>28678623</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>MUCM Toastmasters Club</t>
+          <t>Adducity Toastmasters Club</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2092,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2118,12 +2124,12 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" s="9" t="n">
         <v>0</v>
       </c>
@@ -2137,29 +2143,29 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -2175,15 +2181,15 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>28678623</v>
+        <v>7208725</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Adducity Toastmasters Club</t>
+          <t>Coaches &amp; Trainers Toastmasters Club</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2197,17 +2203,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2223,11 +2229,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P15" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="10" t="n">
-        <v>2</v>
+      <c r="P15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -2242,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X15" s="10" t="n">
-        <v>4</v>
+      <c r="X15" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2260,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
@@ -2280,15 +2286,15 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>7208725</v>
+        <v>28680515</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Coaches &amp; Trainers Toastmasters Club</t>
+          <t>Furamaara Toastmasters Club</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2302,17 +2308,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M16" s="7" t="n">
@@ -2329,7 +2335,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2353,25 +2359,19 @@
         <v>0</v>
       </c>
       <c r="X16" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB16" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB16" s="4" t="n"/>
+      <c r="AC16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2385,15 +2385,15 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>28680515</v>
+        <v>28675333</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Furamaara Toastmasters Club</t>
+          <t>HDC Toastmasters Club</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K17" s="4" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="9" t="n">
         <v>0</v>
@@ -2457,19 +2457,21 @@
       <c r="W17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>0</v>
+      <c r="X17" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="10" t="n">
-        <v>1</v>
+      <c r="Z17" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB17" s="4" t="n"/>
+      <c r="AB17" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="AC17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2484,15 +2486,15 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>28675333</v>
+        <v>28677578</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>HDC Toastmasters Club</t>
+          <t>MUCM Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2506,10 +2508,10 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0</v>
@@ -2533,7 +2535,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>0</v>
@@ -2557,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="X18" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2571,29 +2573,33 @@
       <c r="AB18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>28677578</v>
+        <v>7466771</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>MUCM Advanced Toastmasters Club</t>
+          <t>Bukit Serdang Toastmasters Club</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2607,17 +2613,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M19" s="7" t="n">
@@ -2634,7 +2640,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2643,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" s="9" t="n">
         <v>0</v>
@@ -2652,31 +2658,27 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="10" t="n">
-        <v>1</v>
+      <c r="Z19" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2690,11 +2692,11 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7466771</v>
+        <v>3983</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Bukit Serdang Toastmasters Club</t>
+          <t>CIMA Malaysia Toastmasters Club</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -2712,10 +2714,10 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>1</v>
@@ -2739,7 +2741,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2763,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y20" s="9" t="n">
         <v>0</v>
@@ -2775,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC20" s="4" t="inlineStr"/>
     </row>
@@ -2791,15 +2793,15 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3983</v>
+        <v>989051</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>CIMA Malaysia Toastmasters Club</t>
+          <t>Phoenix Toastmasters Club</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2813,17 +2815,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
@@ -2839,44 +2841,44 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="9" t="n">
-        <v>0</v>
+      <c r="P21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC21" s="4" t="inlineStr"/>
     </row>
@@ -2892,15 +2894,15 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>989051</v>
+        <v>7946370</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Phoenix Toastmasters Club</t>
+          <t>Short &amp; Sweet Toastmasters Club</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2914,17 +2916,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="7" t="n">
@@ -2940,20 +2942,20 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P22" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>2</v>
+      <c r="P22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
@@ -2965,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -2977,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC22" s="4" t="inlineStr"/>
     </row>
@@ -2989,19 +2991,19 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7946370</v>
+        <v>28677247</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Short &amp; Sweet Toastmasters Club</t>
+          <t>Alcon Malaysia Toastmasters Club</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3015,13 +3017,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3053,32 +3055,32 @@
       <c r="S23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="10" t="n">
-        <v>1</v>
+      <c r="T23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X23" s="10" t="n">
-        <v>5</v>
+      <c r="X23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="10" t="n">
-        <v>1</v>
+      <c r="Z23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC23" s="4" t="inlineStr"/>
     </row>
@@ -3094,11 +3096,11 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>28677247</v>
+        <v>28680366</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Alcon Malaysia Toastmasters Club</t>
+          <t>Axrail Toastmasters Club</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -3116,17 +3118,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M24" s="7" t="n">
@@ -3179,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC24" s="4" t="inlineStr"/>
     </row>
@@ -3195,15 +3197,15 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>28680366</v>
+        <v>6588731</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Axrail Toastmasters Club</t>
+          <t>Gasing Hills Toastmasters Club</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3217,17 +3219,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="7" t="n">
@@ -3252,35 +3254,35 @@
       <c r="R25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="9" t="n">
-        <v>0</v>
+      <c r="S25" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X25" s="9" t="n">
-        <v>0</v>
+      <c r="X25" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC25" s="4" t="inlineStr"/>
     </row>
@@ -3296,35 +3298,35 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6588731</v>
+        <v>3730557</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Gasing Hills Toastmasters Club</t>
+          <t>IIUM Toastmasters Club</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>17</v>
-      </c>
       <c r="J26" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -3332,11 +3334,11 @@
         </is>
       </c>
       <c r="M26" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr">
@@ -3353,35 +3355,35 @@
       <c r="R26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" s="10" t="n">
-        <v>1</v>
+      <c r="S26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X26" s="10" t="n">
-        <v>7</v>
+      <c r="X26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="10" t="n">
-        <v>1</v>
+      <c r="Z26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC26" s="4" t="inlineStr"/>
     </row>
@@ -3397,15 +3399,15 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3730557</v>
+        <v>8969</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>IIUM Toastmasters Club</t>
+          <t>Shah Alam Toastmasters Club</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3419,13 +3421,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3433,11 +3435,11 @@
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O27" s="8" t="inlineStr">
@@ -3464,27 +3466,31 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>0</v>
+      <c r="X27" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3494,19 +3500,19 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>8969</v>
+        <v>9150</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Shah Alam Toastmasters Club</t>
+          <t>Crystal Toastmasters Club</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3520,17 +3526,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M28" s="7" t="n">
@@ -3547,7 +3553,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3565,31 +3571,27 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC28" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3603,15 +3605,15 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>9150</v>
+        <v>7564</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Crystal Toastmasters Club</t>
+          <t>D'Utama Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3625,13 +3627,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3652,7 +3654,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3660,23 +3662,23 @@
       <c r="R29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v>0</v>
+      <c r="S29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X29" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y29" s="9" t="n">
         <v>0</v>
@@ -3704,15 +3706,15 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>7564</v>
+        <v>28680912</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>D'Utama Advanced Toastmasters Club</t>
+          <t>EmpowHer Toastmasters Club</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3726,10 +3728,10 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>0</v>
@@ -3761,8 +3763,8 @@
       <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="10" t="n">
-        <v>2</v>
+      <c r="S30" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T30" s="9" t="n">
         <v>0</v>
@@ -3776,21 +3778,19 @@
       <c r="W30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="10" t="n">
-        <v>5</v>
+      <c r="X30" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="10" t="n">
-        <v>1</v>
+      <c r="Z30" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB30" s="4" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -13120,7 +13120,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13160,8 +13160,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P122" s="9" t="n">
-        <v>3</v>
+      <c r="P122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -14247,7 +14247,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14261,13 +14261,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -14305,8 +14305,8 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>3</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -15186,13 +15186,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15871,19 +15871,19 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>28675438</v>
+        <v>28680892</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Central South Malaysia Advanced Toastmasters Club</t>
+          <t>Total Life Planning Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15897,10 +15897,10 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K149" s="4" t="n">
         <v>0</v>
@@ -15947,26 +15947,20 @@
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X149" s="10" t="n">
-        <v>7</v>
+      <c r="X149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="10" t="n">
-        <v>1</v>
+      <c r="Z149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB149" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC149" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AB149" s="4" t="n"/>
+      <c r="AC149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -15980,11 +15974,11 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>1120825</v>
+        <v>28675438</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Eng Choon Huay Kuan Muar Mandarin</t>
+          <t>Central South Malaysia Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
@@ -16065,11 +16059,11 @@
         <v>1</v>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -16085,15 +16079,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>7798</v>
+        <v>1120825</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Historical City Toastmasters Club</t>
+          <t>Eng Choon Huay Kuan Muar Mandarin</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16107,17 +16101,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K151" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L151" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -16136,14 +16130,14 @@
       <c r="P151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" s="10" t="n">
-        <v>2</v>
+      <c r="Q151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S151" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T151" s="9" t="n">
         <v>0</v>
@@ -16158,7 +16152,7 @@
         <v>0</v>
       </c>
       <c r="X151" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -16170,9 +16164,13 @@
         <v>1</v>
       </c>
       <c r="AB151" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC151" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -16186,15 +16184,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>2684647</v>
+        <v>7798</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Pang Clan Association Segamat Mandarin Toastmasters Club</t>
+          <t>Historical City Toastmasters Club</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16208,10 +16206,10 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K152" s="4" t="n">
         <v>0</v>
@@ -16237,14 +16235,14 @@
       <c r="P152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" s="9" t="n">
-        <v>0</v>
+      <c r="Q152" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" s="9" t="n">
         <v>0</v>
@@ -16259,19 +16257,19 @@
         <v>0</v>
       </c>
       <c r="X152" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB152" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="Y152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z152" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA152" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB152" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="AC152" s="4" t="inlineStr"/>
     </row>
@@ -16283,19 +16281,19 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>5553703</v>
+        <v>2684647</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Ampang GBBM Toastmasters Club</t>
+          <t>Pang Clan Association Segamat Mandarin Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16309,10 +16307,10 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K153" s="4" t="n">
         <v>0</v>
@@ -16365,14 +16363,14 @@
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB153" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC153" s="4" t="inlineStr"/>
     </row>
@@ -16388,15 +16386,15 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>5163199</v>
+        <v>5553703</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Cheras Mandarin Toastmasters Club</t>
+          <t>Ampang GBBM Toastmasters Club</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16410,17 +16408,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="7" t="n">
@@ -16436,44 +16434,44 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P154" s="10" t="n">
+      <c r="P154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q154" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V154" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W154" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X154" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="10" t="n">
-        <v>1</v>
+      <c r="Z154" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC154" s="4" t="inlineStr"/>
     </row>
@@ -16489,15 +16487,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>7565673</v>
+        <v>5163199</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Kajang Mandarin Toastmasters Club</t>
+          <t>Cheras Mandarin Toastmasters Club</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16511,25 +16509,25 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M155" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O155" s="8" t="inlineStr">
@@ -16537,17 +16535,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" s="9" t="n">
-        <v>0</v>
+      <c r="P155" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q155" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S155" s="9" t="n">
-        <v>0</v>
+      <c r="S155" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T155" s="9" t="n">
         <v>0</v>
@@ -16555,26 +16553,26 @@
       <c r="U155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V155" s="9" t="n">
-        <v>0</v>
+      <c r="V155" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X155" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X155" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB155" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC155" s="4" t="inlineStr"/>
     </row>
@@ -16590,15 +16588,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>1486176</v>
+        <v>7565673</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Maluri Mandarin Toastmasters Club</t>
+          <t>Kajang Mandarin Toastmasters Club</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16612,13 +16610,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L156" s="8" t="inlineStr">
         <is>
@@ -16626,11 +16624,11 @@
         </is>
       </c>
       <c r="M156" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O156" s="8" t="inlineStr">
@@ -16639,49 +16637,45 @@
         </is>
       </c>
       <c r="P156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q156" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R156" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z156" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA156" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB156" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC156" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -16695,15 +16689,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>5017865</v>
+        <v>1486176</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Seremban Mandarin Toastmasters Club</t>
+          <t>Maluri Mandarin Toastmasters Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16717,13 +16711,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L157" s="8" t="inlineStr">
         <is>
@@ -16746,50 +16740,155 @@
       <c r="P157" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" s="9" t="n">
-        <v>0</v>
+      <c r="Q157" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R157" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T157" s="10" t="n">
-        <v>1</v>
+      <c r="T157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X157" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y157" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB157" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC157" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>5017865</v>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>Seremban Mandarin Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M158" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O158" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P158" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Y157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z157" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA157" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB157" s="4" t="n">
+      <c r="Y158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB158" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC157" s="4" t="inlineStr">
+      <c r="AC158" s="4" t="inlineStr">
         <is>
           <t>Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC157"/>
+  <autoFilter ref="A1:AC158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16800,7 +16899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -16864,25 +16963,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -16891,7 +16990,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -16902,7 +17001,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -16924,7 +17023,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -16935,14 +17034,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16957,7 +17056,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -16968,53 +17067,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -17023,7 +17122,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -17034,26 +17133,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -17067,14 +17166,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17086,10 +17185,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -17100,26 +17199,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -17128,34 +17227,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>1.75</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -17166,20 +17265,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -17188,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -17199,20 +17298,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -17221,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -17232,20 +17331,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -17254,18 +17353,18 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -17298,20 +17397,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -17320,7 +17419,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -17331,20 +17430,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -17353,7 +17452,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -17364,14 +17463,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -17386,31 +17485,31 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -17419,7 +17518,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -17430,14 +17529,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -17463,20 +17562,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -17496,29 +17595,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
         <v>4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -17529,29 +17628,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -17562,20 +17661,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>1.75</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -17584,18 +17683,18 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -17617,7 +17716,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -17628,17 +17727,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
@@ -17647,10 +17746,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -17661,17 +17760,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -17680,10 +17779,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -17694,14 +17793,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17716,25 +17815,25 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17749,7 +17848,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -17760,14 +17859,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -17782,7 +17881,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -17793,14 +17892,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -17826,20 +17925,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -17848,7 +17947,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -17859,20 +17958,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -17881,25 +17980,25 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -17914,7 +18013,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -17925,20 +18024,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -17958,14 +18057,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -17991,17 +18090,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
@@ -18010,47 +18109,14 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I37"/>
+  <autoFilter ref="A1:I36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2880,7 +2884,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3591,7 +3599,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3692,7 +3704,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -5544,7 +5560,11 @@
       <c r="AB47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -6570,7 +6590,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -7178,7 +7202,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7986,7 +8014,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8087,7 +8119,11 @@
       <c r="AB72" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC72" s="4" t="inlineStr"/>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -9006,7 +9042,11 @@
       <c r="AB81" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC81" s="4" t="inlineStr"/>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9826,7 +9866,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -9927,7 +9971,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10129,7 +10177,11 @@
       <c r="AB92" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC92" s="4" t="inlineStr"/>
+      <c r="AC92" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -11050,7 +11102,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11866,7 +11922,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -11967,7 +12027,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -13199,7 +13263,11 @@
       <c r="AB122" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13401,7 +13469,11 @@
       <c r="AB124" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -14120,7 +14192,11 @@
       <c r="AB131" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC131" s="4" t="inlineStr"/>
+      <c r="AC131" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -14528,7 +14604,11 @@
       <c r="AB135" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -15150,7 +15230,11 @@
       <c r="AB141" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC141" s="4" t="inlineStr"/>
+      <c r="AC141" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -15457,7 +15541,11 @@
       <c r="AB144" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC144" s="4" t="inlineStr"/>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -15558,7 +15646,11 @@
       <c r="AB145" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC145" s="4" t="inlineStr"/>
+      <c r="AC145" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -16574,7 +16666,11 @@
       <c r="AB155" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC155" s="4" t="inlineStr"/>
+      <c r="AC155" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">

--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 60 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 57 clubs short</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="9" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2442,8 +2442,8 @@
       <c r="R17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="9" t="n">
-        <v>1</v>
+      <c r="S17" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T17" s="9" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2673,8 +2673,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3668,8 +3668,8 @@
       <c r="P29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" s="9" t="n">
-        <v>0</v>
+      <c r="Q29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3973,8 +3973,8 @@
       <c r="P32" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q32" s="9" t="n">
-        <v>0</v>
+      <c r="Q32" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5135,8 +5135,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q58" s="9" t="n">
         <v>1</v>
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7399,8 +7399,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -8087,7 +8087,7 @@
         <v>2</v>
       </c>
       <c r="R72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" s="9" t="n">
         <v>0</v>
@@ -10318,13 +10318,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10958,8 +10958,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P100" s="9" t="n">
-        <v>3</v>
+      <c r="P100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q100" s="10" t="n">
         <v>2</v>
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>1</v>
@@ -12303,7 +12303,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -13079,7 +13079,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13120,7 +13120,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>1</v>
@@ -13134,8 +13134,8 @@
       <c r="T121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
+      <c r="U121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V121" s="9" t="n">
         <v>0</v>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13550,8 +13550,8 @@
       <c r="T125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U125" s="9" t="n">
-        <v>0</v>
+      <c r="U125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V125" s="9" t="n">
         <v>0</v>
@@ -13816,13 +13816,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -17170,7 +17170,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17203,7 +17203,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -17269,7 +17269,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -17368,7 +17368,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17500,7 +17500,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -17764,13 +17764,13 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -17929,7 +17929,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17962,7 +17962,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 57 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 39 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="9" t="n">
         <v>0</v>
@@ -2049,8 +2049,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2154,8 +2154,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2259,8 +2259,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2445,8 +2445,8 @@
       <c r="S17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2774,8 +2774,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2854,8 +2854,8 @@
       <c r="R21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S21" s="9" t="n">
-        <v>1</v>
+      <c r="S21" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T21" s="10" t="n">
         <v>1</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="9" t="n">
         <v>0</v>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4614,8 +4614,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5240,8 +5240,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5757,8 +5757,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5959,8 +5959,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6060,8 +6060,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6525,13 +6525,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7</v>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>0</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7904,8 +7904,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8516,8 +8516,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8813,8 +8813,8 @@
       <c r="S79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T79" s="9" t="n">
-        <v>0</v>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U79" s="9" t="n">
         <v>0</v>
@@ -9682,7 +9682,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9752,8 +9752,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -10318,13 +10318,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10580,8 +10580,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10611,7 +10611,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -10663,8 +10663,8 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10786,8 +10786,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -11586,7 +11586,7 @@
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="9" t="n">
         <v>0</v>
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13019,7 +13019,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -13048,8 +13048,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -13228,7 +13228,7 @@
         <v>4</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13565,8 +13565,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -14337,17 +14337,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
@@ -14385,7 +14385,7 @@
         <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>4</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" s="9" t="n">
         <v>0</v>
@@ -14881,7 +14881,7 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>0</v>
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15011,8 +15011,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -17071,7 +17071,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -17137,7 +17137,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -17170,7 +17170,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17203,7 +17203,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -17335,7 +17335,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -17368,7 +17368,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -17401,7 +17401,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -17434,7 +17434,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17533,7 +17533,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17599,7 +17599,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17698,7 +17698,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17731,7 +17731,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17929,7 +17929,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17962,7 +17962,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -18043,7 +18043,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -18061,7 +18061,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -892,13 +892,13 @@
         <v>0</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="9" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1312,8 +1312,8 @@
       <c r="S6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="9" t="n">
-        <v>0</v>
+      <c r="T6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="9" t="n">
         <v>0</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="P11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2142,8 +2142,8 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>3</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
         <v>2</v>
       </c>
       <c r="S21" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" s="10" t="n">
         <v>1</v>
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4255,13 +4255,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -5596,13 +5596,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="9" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -5802,13 +5802,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -6105,17 +6105,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -7749,13 +7749,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>0</v>
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9015,8 +9015,8 @@
       <c r="S81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T81" s="9" t="n">
-        <v>0</v>
+      <c r="T81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U81" s="9" t="n">
         <v>0</v>
@@ -9027,8 +9027,8 @@
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="9" t="n">
-        <v>0</v>
+      <c r="X81" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9595,13 +9595,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9696,13 +9696,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -10007,13 +10007,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10655,7 +10655,7 @@
         <v>2</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10932,13 +10932,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -11138,13 +11138,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11445,13 +11445,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11492,8 +11492,8 @@
       <c r="V105" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W105" s="9" t="n">
-        <v>3</v>
+      <c r="W105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -12576,17 +12576,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12621,7 +12621,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -13299,13 +13299,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13843,10 +13843,10 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q128" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -13917,13 +13917,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -15604,7 +15604,7 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -15718,7 +15718,7 @@
         <v>0</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146" s="9" t="n">
         <v>0</v>
@@ -16234,7 +16234,7 @@
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -17013,13 +17013,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -17271,7 +17271,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -17733,7 +17733,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -17898,7 +17898,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17979,7 +17979,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -18063,7 +18063,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/102/inyear.xlsx
+++ b/docs/d/102/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>2</v>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>1</v>
@@ -2437,7 +2437,7 @@
         <v>2</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2860,8 +2860,8 @@
       <c r="T21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
+      <c r="U21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V21" s="10" t="n">
         <v>4</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="10" t="n">
         <v>2</v>
@@ -3680,8 +3680,8 @@
       <c r="T29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U29" s="9" t="n">
-        <v>0</v>
+      <c r="U29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3782,8 +3782,8 @@
       <c r="S30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="9" t="n">
-        <v>0</v>
+      <c r="T30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U30" s="9" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>4</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>0</v>
@@ -5321,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" s="9" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6757,8 +6757,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P59" s="9" t="n">
-        <v>3</v>
+      <c r="P59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q59" s="9" t="n">
         <v>1</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7488,8 +7488,8 @@
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="9" t="n">
-        <v>3</v>
+      <c r="V66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7853,10 +7853,10 @@
         <v>17</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7949,13 +7949,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8193,8 +8193,8 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
@@ -8926,8 +8926,8 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>0</v>
+      <c r="X80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -9389,13 +9389,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -10007,13 +10007,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10199,7 +10199,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10254,8 +10254,8 @@
       <c r="T93" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U93" s="9" t="n">
-        <v>0</v>
+      <c r="U93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V93" s="9" t="n">
         <v>3</v>
@@ -11138,13 +11138,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="10" t="n">
         <v>2</v>
@@ -12000,7 +12000,7 @@
         <v>1</v>
       </c>
       <c r="U110" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V110" s="10" t="n">
         <v>4</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12101,8 +12101,8 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
@@ -12154,7 +12154,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12197,8 +12197,8 @@
       <c r="P112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" s="9" t="n">
-        <v>1</v>
+      <c r="Q112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -13015,7 +13015,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -13849,7 +13849,7 @@
         <v>2</v>
       </c>
       <c r="R128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S128" s="9" t="n">
         <v>0</v>
@@ -14255,7 +14255,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>1</v>
@@ -14525,7 +14525,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14539,13 +14539,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14583,8 +14583,8 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>2</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -17370,13 +17370,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -17568,7 +17568,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17601,7 +17601,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -17667,7 +17667,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -17799,7 +17799,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17931,7 +17931,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -18129,7 +18129,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
